--- a/data/all_datasets/REDD/REDD_House6_stats/2026-04-03.xlsx
+++ b/data/all_datasets/REDD/REDD_House6_stats/2026-04-03.xlsx
@@ -26623,7 +26623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -26821,7 +26821,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -27063,7 +27063,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -27107,7 +27107,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -27547,7 +27547,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E47" t="n">
